--- a/mia07_t3_tra_resultados_trans.xlsx
+++ b/mia07_t3_tra_resultados_trans.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="prob_trans" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="prob_trans" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,684 +417,684 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>NP00000</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>VSIP3S0</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DI0FS0</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>NCFS000</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>SPS00</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>DA0MS0</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>NCMS000</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>AQ0MS0</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>VMP00SM</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Fp</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>VAIP3S0</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>VMP00SF</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>DA0FS0</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>VSIS3S0</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>AQ0CS0</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>RN</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>AQ0FS0</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Z</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>CC</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>VSIP3P0</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>DA0FP0</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>NCFP000</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>VMIS3S0</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>VSN0000</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>PI0MS000</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>DD0MP0</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>NCMP000</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>RG</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>VMP00PM</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>DI0FP0</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>VMN0000</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>PP3FSA00</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Fd</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Fc</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>PI0FS000</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>VASI1S0</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>VAP00SM</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>AO0FS0</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>DP3CP0</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>DI0MS0</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>PR0FS000</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>DP3CS0</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>PD0MS000</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>VMIP3S0</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>VMG0000</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>PP3CNA00</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>VSIF3S0</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>DD0MS0</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>P0000000</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>NCMN000</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>DA0MP0</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>NCCP000</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>VMIP3P0</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>AQ0FP0</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>PR0CN000</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>PP3MPA00</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>DA0NS0</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>AQ0CP0</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>AQ0MP0</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>PR0CS000</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>DI0MP0</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>Fe</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>VMSP3P0</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>PP3CN000</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>Fpa</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>Fpt</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>VMIS3P0</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>VMM03P0</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>PR000000</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>VMII3P0</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>Fx</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>PD0MP000</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>VMIF3P0</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>AO0MS0</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>VSSP1S0</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>PI0CS000</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>NCCS000</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>PR0CP000</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>PP3CSD00</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>VMIC1S0</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>VAIC1S0</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>VSP00SM</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>VMIF3S0</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>VMP00PF</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>VMSP1S0</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>PD0NS000</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>DI0CS0</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>DD0FS0</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>VMIS2S0</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>VAIP3P0</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>PP3FS000</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>VAN0000</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>DD0CS0</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>PP3CPD00</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>VMSI3P0</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>VASP1S0</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>PR0MS000</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>VAII3P0</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>VMIC3P0</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>VMIS1S0</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>PP1CSN00</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>Fs</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>VMM02S0</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>VAIS3S0</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>VMSP2S0</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>Zd</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>NC00000</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>NCMS00D</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>VSIS3P0</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>PP3MS000</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>PI0MP000</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>VMII1S0</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>VAII1S0</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>PD0FS000</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>AQ0CN0</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>VSII1S0</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>PP3NS000</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>VSIC1S0</t>
         </is>
       </c>
-      <c r="DS1" s="1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>VMIP1S0</t>
         </is>
       </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>Zu</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>PT0CS000</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>Fg</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>AO0MP0</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>PT0CN000</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>VMSI1S0</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>DD0CP0</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>DD0FP0</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>PP3FP000</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>NCFN000</t>
         </is>
       </c>
-      <c r="ED1" s="1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>PT0CP000</t>
         </is>
       </c>
-      <c r="EE1" s="1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>Fz</t>
         </is>
       </c>
-      <c r="EF1" s="1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>qF</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>q0</t>
         </is>
@@ -1518,7 +1506,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>NP00000</t>
         </is>
@@ -1930,7 +1918,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>VSIP3S0</t>
         </is>
@@ -2342,7 +2330,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>DI0FS0</t>
         </is>
@@ -2754,7 +2742,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>NCFS000</t>
         </is>
@@ -3166,7 +3154,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>SPS00</t>
         </is>
@@ -3578,7 +3566,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>DA0MS0</t>
         </is>
@@ -3990,7 +3978,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>NCMS000</t>
         </is>
@@ -4402,7 +4390,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>AQ0MS0</t>
         </is>
@@ -4814,7 +4802,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>VMP00SM</t>
         </is>
@@ -5226,7 +5214,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Fp</t>
         </is>
@@ -5638,7 +5626,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>VAIP3S0</t>
         </is>
@@ -6050,7 +6038,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>VMP00SF</t>
         </is>
@@ -6462,7 +6450,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>DA0FS0</t>
         </is>
@@ -6874,7 +6862,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>VSIS3S0</t>
         </is>
@@ -7286,7 +7274,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>AQ0CS0</t>
         </is>
@@ -7698,7 +7686,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>RN</t>
         </is>
@@ -8110,7 +8098,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>AQ0FS0</t>
         </is>
@@ -8522,7 +8510,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Z</t>
         </is>
@@ -8934,7 +8922,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>CC</t>
         </is>
@@ -9346,7 +9334,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>VSIP3P0</t>
         </is>
@@ -9758,7 +9746,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>DA0FP0</t>
         </is>
@@ -10170,7 +10158,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>NCFP000</t>
         </is>
@@ -10582,7 +10570,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
@@ -10994,7 +10982,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>VMIS3S0</t>
         </is>
@@ -11406,7 +11394,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>VSN0000</t>
         </is>
@@ -11818,7 +11806,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>PI0MS000</t>
         </is>
@@ -12230,7 +12218,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>DD0MP0</t>
         </is>
@@ -12642,7 +12630,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>NCMP000</t>
         </is>
@@ -13054,7 +13042,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>RG</t>
         </is>
@@ -13466,7 +13454,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>VMP00PM</t>
         </is>
@@ -13878,7 +13866,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>DI0FP0</t>
         </is>
@@ -14290,7 +14278,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>VMN0000</t>
         </is>
@@ -14702,7 +14690,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>PP3FSA00</t>
         </is>
@@ -15114,7 +15102,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Fd</t>
         </is>
@@ -15526,7 +15514,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Fc</t>
         </is>
@@ -15938,7 +15926,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>PI0FS000</t>
         </is>
@@ -16350,7 +16338,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>VASI1S0</t>
         </is>
@@ -16762,7 +16750,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>VAP00SM</t>
         </is>
@@ -17174,7 +17162,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>AO0FS0</t>
         </is>
@@ -17586,7 +17574,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>DP3CP0</t>
         </is>
@@ -17998,7 +17986,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>DI0MS0</t>
         </is>
@@ -18410,7 +18398,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>PR0FS000</t>
         </is>
@@ -18822,7 +18810,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>DP3CS0</t>
         </is>
@@ -19234,7 +19222,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>PD0MS000</t>
         </is>
@@ -19646,7 +19634,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>VMIP3S0</t>
         </is>
@@ -20058,7 +20046,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>VMG0000</t>
         </is>
@@ -20470,7 +20458,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="inlineStr">
+      <c r="A49" t="inlineStr">
         <is>
           <t>PP3CNA00</t>
         </is>
@@ -20882,7 +20870,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="inlineStr">
+      <c r="A50" t="inlineStr">
         <is>
           <t>VSIF3S0</t>
         </is>
@@ -21294,7 +21282,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="inlineStr">
+      <c r="A51" t="inlineStr">
         <is>
           <t>DD0MS0</t>
         </is>
@@ -21706,7 +21694,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="inlineStr">
+      <c r="A52" t="inlineStr">
         <is>
           <t>P0000000</t>
         </is>
@@ -22118,7 +22106,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="inlineStr">
+      <c r="A53" t="inlineStr">
         <is>
           <t>W</t>
         </is>
@@ -22530,7 +22518,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="inlineStr">
+      <c r="A54" t="inlineStr">
         <is>
           <t>NCMN000</t>
         </is>
@@ -22942,7 +22930,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="inlineStr">
+      <c r="A55" t="inlineStr">
         <is>
           <t>DA0MP0</t>
         </is>
@@ -23354,7 +23342,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="inlineStr">
+      <c r="A56" t="inlineStr">
         <is>
           <t>NCCP000</t>
         </is>
@@ -23766,7 +23754,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="inlineStr">
+      <c r="A57" t="inlineStr">
         <is>
           <t>VMIP3P0</t>
         </is>
@@ -24178,7 +24166,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="inlineStr">
+      <c r="A58" t="inlineStr">
         <is>
           <t>AQ0FP0</t>
         </is>
@@ -24590,7 +24578,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="inlineStr">
+      <c r="A59" t="inlineStr">
         <is>
           <t>PR0CN000</t>
         </is>
@@ -25002,7 +24990,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="inlineStr">
+      <c r="A60" t="inlineStr">
         <is>
           <t>PP3MPA00</t>
         </is>
@@ -25414,7 +25402,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="inlineStr">
+      <c r="A61" t="inlineStr">
         <is>
           <t>DA0NS0</t>
         </is>
@@ -25826,7 +25814,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="inlineStr">
+      <c r="A62" t="inlineStr">
         <is>
           <t>AQ0CP0</t>
         </is>
@@ -26238,7 +26226,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="inlineStr">
+      <c r="A63" t="inlineStr">
         <is>
           <t>AQ0MP0</t>
         </is>
@@ -26650,7 +26638,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="inlineStr">
+      <c r="A64" t="inlineStr">
         <is>
           <t>PR0CS000</t>
         </is>
@@ -27062,7 +27050,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="inlineStr">
+      <c r="A65" t="inlineStr">
         <is>
           <t>DI0MP0</t>
         </is>
@@ -27474,7 +27462,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="inlineStr">
+      <c r="A66" t="inlineStr">
         <is>
           <t>Fe</t>
         </is>
@@ -27886,7 +27874,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="inlineStr">
+      <c r="A67" t="inlineStr">
         <is>
           <t>VMSP3P0</t>
         </is>
@@ -28298,7 +28286,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="inlineStr">
+      <c r="A68" t="inlineStr">
         <is>
           <t>PP3CN000</t>
         </is>
@@ -28710,7 +28698,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="inlineStr">
+      <c r="A69" t="inlineStr">
         <is>
           <t>Fpa</t>
         </is>
@@ -29122,7 +29110,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="inlineStr">
+      <c r="A70" t="inlineStr">
         <is>
           <t>Fpt</t>
         </is>
@@ -29534,7 +29522,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="inlineStr">
+      <c r="A71" t="inlineStr">
         <is>
           <t>VMIS3P0</t>
         </is>
@@ -29946,7 +29934,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="inlineStr">
+      <c r="A72" t="inlineStr">
         <is>
           <t>VMM03P0</t>
         </is>
@@ -30358,7 +30346,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="inlineStr">
+      <c r="A73" t="inlineStr">
         <is>
           <t>PR000000</t>
         </is>
@@ -30770,7 +30758,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="inlineStr">
+      <c r="A74" t="inlineStr">
         <is>
           <t>VMII3P0</t>
         </is>
@@ -31182,7 +31170,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="inlineStr">
+      <c r="A75" t="inlineStr">
         <is>
           <t>Fx</t>
         </is>
@@ -31594,7 +31582,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="inlineStr">
+      <c r="A76" t="inlineStr">
         <is>
           <t>PD0MP000</t>
         </is>
@@ -32006,7 +31994,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="inlineStr">
+      <c r="A77" t="inlineStr">
         <is>
           <t>VMIF3P0</t>
         </is>
@@ -32418,7 +32406,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="inlineStr">
+      <c r="A78" t="inlineStr">
         <is>
           <t>AO0MS0</t>
         </is>
@@ -32830,7 +32818,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="inlineStr">
+      <c r="A79" t="inlineStr">
         <is>
           <t>VSSP1S0</t>
         </is>
@@ -33242,7 +33230,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="inlineStr">
+      <c r="A80" t="inlineStr">
         <is>
           <t>PI0CS000</t>
         </is>
@@ -33654,7 +33642,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="inlineStr">
+      <c r="A81" t="inlineStr">
         <is>
           <t>NCCS000</t>
         </is>
@@ -34066,7 +34054,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="inlineStr">
+      <c r="A82" t="inlineStr">
         <is>
           <t>PR0CP000</t>
         </is>
@@ -34478,7 +34466,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="inlineStr">
+      <c r="A83" t="inlineStr">
         <is>
           <t>PP3CSD00</t>
         </is>
@@ -34890,7 +34878,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="inlineStr">
+      <c r="A84" t="inlineStr">
         <is>
           <t>VMIC1S0</t>
         </is>
@@ -35302,7 +35290,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="inlineStr">
+      <c r="A85" t="inlineStr">
         <is>
           <t>VAIC1S0</t>
         </is>
@@ -35714,7 +35702,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="inlineStr">
+      <c r="A86" t="inlineStr">
         <is>
           <t>VSP00SM</t>
         </is>
@@ -36126,7 +36114,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="inlineStr">
+      <c r="A87" t="inlineStr">
         <is>
           <t>VMIF3S0</t>
         </is>
@@ -36538,7 +36526,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="inlineStr">
+      <c r="A88" t="inlineStr">
         <is>
           <t>VMP00PF</t>
         </is>
@@ -36950,7 +36938,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="inlineStr">
+      <c r="A89" t="inlineStr">
         <is>
           <t>VMSP1S0</t>
         </is>
@@ -37362,7 +37350,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="inlineStr">
+      <c r="A90" t="inlineStr">
         <is>
           <t>PD0NS000</t>
         </is>
@@ -37774,7 +37762,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="inlineStr">
+      <c r="A91" t="inlineStr">
         <is>
           <t>DI0CS0</t>
         </is>
@@ -38186,7 +38174,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="inlineStr">
+      <c r="A92" t="inlineStr">
         <is>
           <t>DD0FS0</t>
         </is>
@@ -38598,7 +38586,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="inlineStr">
+      <c r="A93" t="inlineStr">
         <is>
           <t>VMIS2S0</t>
         </is>
@@ -39010,7 +38998,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="inlineStr">
+      <c r="A94" t="inlineStr">
         <is>
           <t>VAIP3P0</t>
         </is>
@@ -39422,7 +39410,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="inlineStr">
+      <c r="A95" t="inlineStr">
         <is>
           <t>PP3FS000</t>
         </is>
@@ -39834,7 +39822,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="inlineStr">
+      <c r="A96" t="inlineStr">
         <is>
           <t>VAN0000</t>
         </is>
@@ -40246,7 +40234,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="inlineStr">
+      <c r="A97" t="inlineStr">
         <is>
           <t>DD0CS0</t>
         </is>
@@ -40658,7 +40646,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="inlineStr">
+      <c r="A98" t="inlineStr">
         <is>
           <t>PP3CPD00</t>
         </is>
@@ -41070,7 +41058,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="inlineStr">
+      <c r="A99" t="inlineStr">
         <is>
           <t>VMSI3P0</t>
         </is>
@@ -41482,7 +41470,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="inlineStr">
+      <c r="A100" t="inlineStr">
         <is>
           <t>VASP1S0</t>
         </is>
@@ -41894,7 +41882,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="inlineStr">
+      <c r="A101" t="inlineStr">
         <is>
           <t>PR0MS000</t>
         </is>
@@ -42306,7 +42294,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="inlineStr">
+      <c r="A102" t="inlineStr">
         <is>
           <t>VAII3P0</t>
         </is>
@@ -42718,7 +42706,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="inlineStr">
+      <c r="A103" t="inlineStr">
         <is>
           <t>VMIC3P0</t>
         </is>
@@ -43130,7 +43118,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="inlineStr">
+      <c r="A104" t="inlineStr">
         <is>
           <t>VMIS1S0</t>
         </is>
@@ -43542,7 +43530,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="inlineStr">
+      <c r="A105" t="inlineStr">
         <is>
           <t>PP1CSN00</t>
         </is>
@@ -43954,7 +43942,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="inlineStr">
+      <c r="A106" t="inlineStr">
         <is>
           <t>Fs</t>
         </is>
@@ -44366,7 +44354,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="inlineStr">
+      <c r="A107" t="inlineStr">
         <is>
           <t>VMM02S0</t>
         </is>
@@ -44778,7 +44766,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="inlineStr">
+      <c r="A108" t="inlineStr">
         <is>
           <t>VAIS3S0</t>
         </is>
@@ -45190,7 +45178,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="inlineStr">
+      <c r="A109" t="inlineStr">
         <is>
           <t>VMSP2S0</t>
         </is>
@@ -45602,7 +45590,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="inlineStr">
+      <c r="A110" t="inlineStr">
         <is>
           <t>Zd</t>
         </is>
@@ -46014,7 +46002,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="inlineStr">
+      <c r="A111" t="inlineStr">
         <is>
           <t>NC00000</t>
         </is>
@@ -46426,7 +46414,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="inlineStr">
+      <c r="A112" t="inlineStr">
         <is>
           <t>NCMS00D</t>
         </is>
@@ -46838,7 +46826,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="inlineStr">
+      <c r="A113" t="inlineStr">
         <is>
           <t>VSIS3P0</t>
         </is>
@@ -47250,7 +47238,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="inlineStr">
+      <c r="A114" t="inlineStr">
         <is>
           <t>PP3MS000</t>
         </is>
@@ -47662,7 +47650,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="inlineStr">
+      <c r="A115" t="inlineStr">
         <is>
           <t>PI0MP000</t>
         </is>
@@ -48074,7 +48062,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="inlineStr">
+      <c r="A116" t="inlineStr">
         <is>
           <t>VMII1S0</t>
         </is>
@@ -48486,7 +48474,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="inlineStr">
+      <c r="A117" t="inlineStr">
         <is>
           <t>VAII1S0</t>
         </is>
@@ -48898,7 +48886,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="inlineStr">
+      <c r="A118" t="inlineStr">
         <is>
           <t>PD0FS000</t>
         </is>
@@ -49310,7 +49298,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="inlineStr">
+      <c r="A119" t="inlineStr">
         <is>
           <t>AQ0CN0</t>
         </is>
@@ -49722,7 +49710,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="inlineStr">
+      <c r="A120" t="inlineStr">
         <is>
           <t>I</t>
         </is>
@@ -50134,7 +50122,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="inlineStr">
+      <c r="A121" t="inlineStr">
         <is>
           <t>VSII1S0</t>
         </is>
@@ -50546,7 +50534,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="inlineStr">
+      <c r="A122" t="inlineStr">
         <is>
           <t>PP3NS000</t>
         </is>
@@ -50958,7 +50946,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="inlineStr">
+      <c r="A123" t="inlineStr">
         <is>
           <t>VSIC1S0</t>
         </is>
@@ -51370,7 +51358,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="inlineStr">
+      <c r="A124" t="inlineStr">
         <is>
           <t>VMIP1S0</t>
         </is>
@@ -51782,7 +51770,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="inlineStr">
+      <c r="A125" t="inlineStr">
         <is>
           <t>Zu</t>
         </is>
@@ -52194,7 +52182,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="inlineStr">
+      <c r="A126" t="inlineStr">
         <is>
           <t>PT0CS000</t>
         </is>
@@ -52606,7 +52594,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="inlineStr">
+      <c r="A127" t="inlineStr">
         <is>
           <t>Fg</t>
         </is>
@@ -53018,7 +53006,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="inlineStr">
+      <c r="A128" t="inlineStr">
         <is>
           <t>AO0MP0</t>
         </is>
@@ -53430,7 +53418,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="inlineStr">
+      <c r="A129" t="inlineStr">
         <is>
           <t>PT0CN000</t>
         </is>
@@ -53842,7 +53830,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="inlineStr">
+      <c r="A130" t="inlineStr">
         <is>
           <t>VMSI1S0</t>
         </is>
@@ -54254,7 +54242,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="inlineStr">
+      <c r="A131" t="inlineStr">
         <is>
           <t>DD0CP0</t>
         </is>
@@ -54666,7 +54654,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="inlineStr">
+      <c r="A132" t="inlineStr">
         <is>
           <t>DD0FP0</t>
         </is>
@@ -55078,7 +55066,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="inlineStr">
+      <c r="A133" t="inlineStr">
         <is>
           <t>PP3FP000</t>
         </is>
@@ -55490,7 +55478,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="inlineStr">
+      <c r="A134" t="inlineStr">
         <is>
           <t>NCFN000</t>
         </is>
@@ -55902,7 +55890,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="inlineStr">
+      <c r="A135" t="inlineStr">
         <is>
           <t>PT0CP000</t>
         </is>
@@ -56314,7 +56302,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="inlineStr">
+      <c r="A136" t="inlineStr">
         <is>
           <t>Fz</t>
         </is>
